--- a/data/Recruitment_Requisition.xlsx
+++ b/data/Recruitment_Requisition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kubotagroup-my.sharepoint.com/personal/lapat_j_kubota_com/Documents/Documents/Recruitment Tools/Dashboard Data Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3688" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E59AC3-9731-4A98-AB00-90DF33F6F125}"/>
+  <xr:revisionPtr revIDLastSave="3691" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7549731B-2996-4F18-AF78-38F8A2DE8FC4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5982D4A9-2AD8-4F8A-AE0B-0D729A27807E}"/>
   </bookViews>
@@ -16166,7 +16166,7 @@
         <v>377</v>
       </c>
       <c r="X113" s="70" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="Y113" s="74"/>
       <c r="Z113" s="71" t="s">
@@ -16604,7 +16604,7 @@
         <v>46281</v>
       </c>
       <c r="X117" s="97" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="Y117" s="101"/>
       <c r="Z117" s="96"/>
@@ -16714,7 +16714,7 @@
         <v>46281</v>
       </c>
       <c r="X118" s="97" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="Y118" s="101"/>
       <c r="Z118" s="96"/>

--- a/data/Recruitment_Requisition.xlsx
+++ b/data/Recruitment_Requisition.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kubotagroup-my.sharepoint.com/personal/lapat_j_kubota_com/Documents/Documents/Recruitment Tools/Dashboard Data Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3691" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7549731B-2996-4F18-AF78-38F8A2DE8FC4}"/>
+  <xr:revisionPtr revIDLastSave="3738" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C3390D3-D864-45CC-8BC8-CE1192F51FF9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5982D4A9-2AD8-4F8A-AE0B-0D729A27807E}"/>
   </bookViews>
@@ -148,12 +148,45 @@
         </r>
       </text>
     </comment>
+    <comment ref="D124" authorId="1" shapeId="0" xr:uid="{07BB29B8-BC30-4239-9DB7-1789A955AAA4}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="222"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Lapat Jitwongwai (Jitwongwai Lapat):
+รอโยกย้ายจาก SKL
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D125" authorId="1" shapeId="0" xr:uid="{F6C1F27C-BBF3-483C-8674-544DDC39DDFF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="222"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Lapat Jitwongwai (Jitwongwai Lapat):
+SUb&gt;R</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1964" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1973" uniqueCount="622">
   <si>
     <t>Year</t>
   </si>
@@ -1140,6 +1173,9 @@
   </si>
   <si>
     <t>Wait to Join</t>
+  </si>
+  <si>
+    <t>นพธนดนย์ ชินวงศ์สกุล</t>
   </si>
   <si>
     <t>Nov,1 2026</t>
@@ -1414,6 +1450,9 @@
     <t>Human Resources Development</t>
   </si>
   <si>
+    <t>Final Interview</t>
+  </si>
+  <si>
     <t>Marketing / Engineer</t>
   </si>
   <si>
@@ -1426,15 +1465,15 @@
     <t>Overseas service Creativity</t>
   </si>
   <si>
-    <t>Final Interview</t>
-  </si>
-  <si>
     <t>Scholarship</t>
   </si>
   <si>
     <t>อัมพวา ธรรมอุดมพร</t>
   </si>
   <si>
+    <t>ยศพัทธ์ อนันต์กิจตระกูล</t>
+  </si>
+  <si>
     <t>พัฒนาโปรแกรมบริการ,วิเคราะห์ข้อมูลและตลาด,ทำงานร่วมกับทีมท้องถิ่นและพาร์ตเนอร์ เพื่อปรับใช้แผนการตลาด</t>
   </si>
   <si>
@@ -1451,12 +1490,6 @@
   </si>
   <si>
     <t>Sales Engineer</t>
-  </si>
-  <si>
-    <t>รอโยกย้ายคนจาก SKL</t>
-  </si>
-  <si>
-    <t>Sub&gt;R</t>
   </si>
   <si>
     <t>Holidays</t>
@@ -5143,9 +5176,10 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}" name="Master" displayName="Master" ref="A1:AI125" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52" tableBorderDxfId="51">
   <autoFilter ref="A1:AI125" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}">
-    <filterColumn colId="23">
+    <filterColumn colId="11">
       <filters>
-        <filter val="Under Review"/>
+        <filter val="Final Interview"/>
+        <filter val="Screening"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -5710,7 +5744,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="2" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A2" s="46">
         <v>2024</v>
       </c>
@@ -5808,7 +5842,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="8"/>
     </row>
-    <row r="3" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="3" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A3" s="46">
         <v>2024</v>
       </c>
@@ -5900,7 +5934,7 @@
       <c r="AH3" s="12"/>
       <c r="AI3" s="8"/>
     </row>
-    <row r="4" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="4" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A4" s="46">
         <v>2024</v>
       </c>
@@ -5988,7 +6022,7 @@
       <c r="AH4" s="12"/>
       <c r="AI4" s="8"/>
     </row>
-    <row r="5" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="5" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A5" s="46">
         <v>2024</v>
       </c>
@@ -6078,7 +6112,7 @@
       <c r="AH5" s="12"/>
       <c r="AI5" s="8"/>
     </row>
-    <row r="6" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="6" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A6" s="46">
         <v>2024</v>
       </c>
@@ -6166,7 +6200,7 @@
       <c r="AH6" s="12"/>
       <c r="AI6" s="8"/>
     </row>
-    <row r="7" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="7" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A7" s="46">
         <v>2024</v>
       </c>
@@ -6254,7 +6288,7 @@
       <c r="AH7" s="12"/>
       <c r="AI7" s="8"/>
     </row>
-    <row r="8" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="8" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A8" s="46">
         <v>2024</v>
       </c>
@@ -6346,7 +6380,7 @@
       <c r="AH8" s="12"/>
       <c r="AI8" s="8"/>
     </row>
-    <row r="9" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="9" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A9" s="46">
         <v>2024</v>
       </c>
@@ -6432,7 +6466,7 @@
       <c r="AH9" s="12"/>
       <c r="AI9" s="8"/>
     </row>
-    <row r="10" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="10" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A10" s="46">
         <v>2024</v>
       </c>
@@ -6520,7 +6554,7 @@
       <c r="AH10" s="12"/>
       <c r="AI10" s="8"/>
     </row>
-    <row r="11" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="11" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A11" s="46">
         <v>2024</v>
       </c>
@@ -6610,7 +6644,7 @@
       <c r="AH11" s="12"/>
       <c r="AI11" s="8"/>
     </row>
-    <row r="12" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="12" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A12" s="46">
         <v>2024</v>
       </c>
@@ -6698,7 +6732,7 @@
       <c r="AH12" s="12"/>
       <c r="AI12" s="8"/>
     </row>
-    <row r="13" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="13" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A13" s="46">
         <v>2024</v>
       </c>
@@ -6788,7 +6822,7 @@
       <c r="AH13" s="12"/>
       <c r="AI13" s="8"/>
     </row>
-    <row r="14" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="14" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A14" s="46">
         <v>2024</v>
       </c>
@@ -6878,7 +6912,7 @@
       <c r="AH14" s="12"/>
       <c r="AI14" s="8"/>
     </row>
-    <row r="15" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="15" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A15" s="46">
         <v>2024</v>
       </c>
@@ -6966,7 +7000,7 @@
       <c r="AH15" s="12"/>
       <c r="AI15" s="8"/>
     </row>
-    <row r="16" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="16" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A16" s="46">
         <v>2024</v>
       </c>
@@ -7056,7 +7090,7 @@
       <c r="AH16" s="12"/>
       <c r="AI16" s="8"/>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A17" s="46">
         <v>2024</v>
       </c>
@@ -7144,7 +7178,7 @@
       <c r="AH17" s="12"/>
       <c r="AI17" s="8"/>
     </row>
-    <row r="18" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="18" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A18" s="46">
         <v>2024</v>
       </c>
@@ -7234,7 +7268,7 @@
       <c r="AH18" s="12"/>
       <c r="AI18" s="8"/>
     </row>
-    <row r="19" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="19" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A19" s="46">
         <v>2024</v>
       </c>
@@ -7324,7 +7358,7 @@
       <c r="AH19" s="12"/>
       <c r="AI19" s="8"/>
     </row>
-    <row r="20" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="20" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A20" s="46">
         <v>2024</v>
       </c>
@@ -7414,7 +7448,7 @@
       <c r="AH20" s="12"/>
       <c r="AI20" s="8"/>
     </row>
-    <row r="21" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="21" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A21" s="46">
         <v>2025</v>
       </c>
@@ -7506,7 +7540,7 @@
       <c r="AH21" s="12"/>
       <c r="AI21" s="8"/>
     </row>
-    <row r="22" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="22" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A22" s="46">
         <v>2025</v>
       </c>
@@ -7598,7 +7632,7 @@
       <c r="AH22" s="12"/>
       <c r="AI22" s="8"/>
     </row>
-    <row r="23" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="23" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A23" s="46">
         <v>2025</v>
       </c>
@@ -7690,7 +7724,7 @@
       <c r="AH23" s="12"/>
       <c r="AI23" s="8"/>
     </row>
-    <row r="24" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="24" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A24" s="46">
         <v>2025</v>
       </c>
@@ -7782,7 +7816,7 @@
       <c r="AH24" s="12"/>
       <c r="AI24" s="8"/>
     </row>
-    <row r="25" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="25" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A25" s="46">
         <v>2025</v>
       </c>
@@ -7874,7 +7908,7 @@
       <c r="AH25" s="12"/>
       <c r="AI25" s="8"/>
     </row>
-    <row r="26" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="26" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A26" s="46">
         <v>2025</v>
       </c>
@@ -7966,7 +8000,7 @@
       <c r="AH26" s="12"/>
       <c r="AI26" s="8"/>
     </row>
-    <row r="27" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="27" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A27" s="46">
         <v>2025</v>
       </c>
@@ -8058,7 +8092,7 @@
       <c r="AH27" s="12"/>
       <c r="AI27" s="8"/>
     </row>
-    <row r="28" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="28" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A28" s="46">
         <v>2025</v>
       </c>
@@ -8152,7 +8186,7 @@
       <c r="AH28" s="12"/>
       <c r="AI28" s="8"/>
     </row>
-    <row r="29" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="29" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A29" s="46">
         <v>2025</v>
       </c>
@@ -8244,7 +8278,7 @@
       <c r="AH29" s="12"/>
       <c r="AI29" s="8"/>
     </row>
-    <row r="30" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="30" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A30" s="46">
         <v>2025</v>
       </c>
@@ -8338,7 +8372,7 @@
       <c r="AH30" s="12"/>
       <c r="AI30" s="8"/>
     </row>
-    <row r="31" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="31" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A31" s="46">
         <v>2025</v>
       </c>
@@ -8436,7 +8470,7 @@
       <c r="AH31" s="12"/>
       <c r="AI31" s="8"/>
     </row>
-    <row r="32" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="32" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A32" s="46">
         <v>2025</v>
       </c>
@@ -8530,7 +8564,7 @@
       <c r="AH32" s="12"/>
       <c r="AI32" s="8"/>
     </row>
-    <row r="33" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="33" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A33" s="46">
         <v>2025</v>
       </c>
@@ -8622,7 +8656,7 @@
       <c r="AH33" s="12"/>
       <c r="AI33" s="8"/>
     </row>
-    <row r="34" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="34" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A34" s="46">
         <v>2025</v>
       </c>
@@ -8722,7 +8756,7 @@
       <c r="AH34" s="12"/>
       <c r="AI34" s="8"/>
     </row>
-    <row r="35" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="35" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A35" s="46">
         <v>2025</v>
       </c>
@@ -8816,7 +8850,7 @@
       <c r="AH35" s="12"/>
       <c r="AI35" s="8"/>
     </row>
-    <row r="36" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="36" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A36" s="46">
         <v>2025</v>
       </c>
@@ -8910,7 +8944,7 @@
       <c r="AH36" s="12"/>
       <c r="AI36" s="8"/>
     </row>
-    <row r="37" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="37" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A37" s="46">
         <v>2025</v>
       </c>
@@ -8969,7 +9003,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="Q37" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -8994,7 +9028,7 @@
       <c r="AH37" s="12"/>
       <c r="AI37" s="8"/>
     </row>
-    <row r="38" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="38" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A38" s="46">
         <v>2025</v>
       </c>
@@ -9086,7 +9120,7 @@
       <c r="AH38" s="12"/>
       <c r="AI38" s="8"/>
     </row>
-    <row r="39" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="39" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A39" s="46">
         <v>2025</v>
       </c>
@@ -9176,7 +9210,7 @@
       <c r="AH39" s="12"/>
       <c r="AI39" s="8"/>
     </row>
-    <row r="40" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="40" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A40" s="46">
         <v>2025</v>
       </c>
@@ -9266,7 +9300,7 @@
       <c r="AH40" s="12"/>
       <c r="AI40" s="8"/>
     </row>
-    <row r="41" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="41" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A41" s="46">
         <v>2025</v>
       </c>
@@ -9358,7 +9392,7 @@
       <c r="AH41" s="12"/>
       <c r="AI41" s="8"/>
     </row>
-    <row r="42" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="42" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A42" s="46">
         <v>2025</v>
       </c>
@@ -9450,7 +9484,7 @@
       <c r="AH42" s="12"/>
       <c r="AI42" s="8"/>
     </row>
-    <row r="43" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="43" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A43" s="46">
         <v>2025</v>
       </c>
@@ -9542,7 +9576,7 @@
       <c r="AH43" s="12"/>
       <c r="AI43" s="8"/>
     </row>
-    <row r="44" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="44" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A44" s="46">
         <v>2025</v>
       </c>
@@ -9634,7 +9668,7 @@
       <c r="AH44" s="12"/>
       <c r="AI44" s="8"/>
     </row>
-    <row r="45" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="45" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A45" s="46">
         <v>2025</v>
       </c>
@@ -9726,7 +9760,7 @@
       <c r="AH45" s="12"/>
       <c r="AI45" s="8"/>
     </row>
-    <row r="46" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="46" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A46" s="46">
         <v>2025</v>
       </c>
@@ -9818,7 +9852,7 @@
       <c r="AH46" s="12"/>
       <c r="AI46" s="8"/>
     </row>
-    <row r="47" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="47" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A47" s="46">
         <v>2025</v>
       </c>
@@ -9906,7 +9940,7 @@
       <c r="AH47" s="12"/>
       <c r="AI47" s="8"/>
     </row>
-    <row r="48" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="48" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A48" s="46">
         <v>2025</v>
       </c>
@@ -10002,7 +10036,7 @@
       <c r="AH48" s="12"/>
       <c r="AI48" s="8"/>
     </row>
-    <row r="49" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="49" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A49" s="46">
         <v>2025</v>
       </c>
@@ -10096,7 +10130,7 @@
       <c r="AH49" s="12"/>
       <c r="AI49" s="8"/>
     </row>
-    <row r="50" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="50" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A50" s="46">
         <v>2025</v>
       </c>
@@ -10188,7 +10222,7 @@
       <c r="AH50" s="12"/>
       <c r="AI50" s="8"/>
     </row>
-    <row r="51" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="51" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A51" s="46">
         <v>2025</v>
       </c>
@@ -10280,7 +10314,7 @@
       <c r="AH51" s="12"/>
       <c r="AI51" s="8"/>
     </row>
-    <row r="52" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="52" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A52" s="46">
         <v>2025</v>
       </c>
@@ -10372,7 +10406,7 @@
       <c r="AH52" s="12"/>
       <c r="AI52" s="8"/>
     </row>
-    <row r="53" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="53" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A53" s="46">
         <v>2025</v>
       </c>
@@ -10460,7 +10494,7 @@
       <c r="AH53" s="12"/>
       <c r="AI53" s="8"/>
     </row>
-    <row r="54" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="54" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A54" s="46">
         <v>2025</v>
       </c>
@@ -10550,7 +10584,7 @@
       <c r="AH54" s="12"/>
       <c r="AI54" s="8"/>
     </row>
-    <row r="55" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="55" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A55" s="46">
         <v>2025</v>
       </c>
@@ -10640,7 +10674,7 @@
       <c r="AH55" s="12"/>
       <c r="AI55" s="8"/>
     </row>
-    <row r="56" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="56" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A56" s="46">
         <v>2025</v>
       </c>
@@ -10728,7 +10762,7 @@
       <c r="AH56" s="12"/>
       <c r="AI56" s="8"/>
     </row>
-    <row r="57" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="57" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A57" s="46">
         <v>2025</v>
       </c>
@@ -10816,7 +10850,7 @@
       <c r="AH57" s="12"/>
       <c r="AI57" s="8"/>
     </row>
-    <row r="58" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="58" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A58" s="46">
         <v>2025</v>
       </c>
@@ -10910,7 +10944,7 @@
       <c r="AH58" s="12"/>
       <c r="AI58" s="8"/>
     </row>
-    <row r="59" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="59" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A59" s="46">
         <v>2025</v>
       </c>
@@ -11004,7 +11038,7 @@
       <c r="AH59" s="12"/>
       <c r="AI59" s="8"/>
     </row>
-    <row r="60" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="60" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A60" s="46">
         <v>2025</v>
       </c>
@@ -11098,7 +11132,7 @@
       <c r="AH60" s="12"/>
       <c r="AI60" s="8"/>
     </row>
-    <row r="61" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="61" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A61" s="46">
         <v>2025</v>
       </c>
@@ -11188,7 +11222,7 @@
       <c r="AH61" s="12"/>
       <c r="AI61" s="8"/>
     </row>
-    <row r="62" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="62" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A62" s="46">
         <v>2025</v>
       </c>
@@ -11278,7 +11312,7 @@
       <c r="AH62" s="12"/>
       <c r="AI62" s="8"/>
     </row>
-    <row r="63" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="63" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A63" s="46">
         <v>2025</v>
       </c>
@@ -11368,7 +11402,7 @@
       <c r="AH63" s="12"/>
       <c r="AI63" s="8"/>
     </row>
-    <row r="64" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="64" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A64" s="46">
         <v>2025</v>
       </c>
@@ -11462,7 +11496,7 @@
       <c r="AH64" s="12"/>
       <c r="AI64" s="8"/>
     </row>
-    <row r="65" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="65" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A65" s="46">
         <v>2025</v>
       </c>
@@ -11556,7 +11590,7 @@
       <c r="AH65" s="12"/>
       <c r="AI65" s="8"/>
     </row>
-    <row r="66" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="66" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A66" s="46">
         <v>2025</v>
       </c>
@@ -11658,7 +11692,7 @@
       <c r="AH66" s="12"/>
       <c r="AI66" s="8"/>
     </row>
-    <row r="67" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="67" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A67" s="46">
         <v>2025</v>
       </c>
@@ -11750,7 +11784,7 @@
       <c r="AH67" s="12"/>
       <c r="AI67" s="8"/>
     </row>
-    <row r="68" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="68" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A68" s="46">
         <v>2025</v>
       </c>
@@ -11842,7 +11876,7 @@
       <c r="AH68" s="12"/>
       <c r="AI68" s="8"/>
     </row>
-    <row r="69" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="69" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A69" s="46">
         <v>2025</v>
       </c>
@@ -11934,7 +11968,7 @@
       <c r="AH69" s="12"/>
       <c r="AI69" s="8"/>
     </row>
-    <row r="70" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="70" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A70" s="46">
         <v>2025</v>
       </c>
@@ -11995,7 +12029,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="Q70" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -12024,7 +12058,7 @@
       <c r="AH70" s="12"/>
       <c r="AI70" s="8"/>
     </row>
-    <row r="71" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="71" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A71" s="46">
         <v>2025</v>
       </c>
@@ -12118,7 +12152,7 @@
       <c r="AH71" s="12"/>
       <c r="AI71" s="8"/>
     </row>
-    <row r="72" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="72" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A72" s="46">
         <v>2025</v>
       </c>
@@ -12212,7 +12246,7 @@
       <c r="AH72" s="12"/>
       <c r="AI72" s="8"/>
     </row>
-    <row r="73" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="73" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A73" s="46">
         <v>2025</v>
       </c>
@@ -12306,7 +12340,7 @@
       <c r="AH73" s="12"/>
       <c r="AI73" s="8"/>
     </row>
-    <row r="74" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="74" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A74" s="46">
         <v>2025</v>
       </c>
@@ -12400,7 +12434,7 @@
       <c r="AH74" s="12"/>
       <c r="AI74" s="8"/>
     </row>
-    <row r="75" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="75" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A75" s="46">
         <v>2025</v>
       </c>
@@ -12496,7 +12530,7 @@
       <c r="AH75" s="12"/>
       <c r="AI75" s="8"/>
     </row>
-    <row r="76" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="76" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A76" s="46">
         <v>2025</v>
       </c>
@@ -12590,7 +12624,7 @@
       <c r="AH76" s="17"/>
       <c r="AI76" s="8"/>
     </row>
-    <row r="77" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="77" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A77" s="46">
         <v>2025</v>
       </c>
@@ -12688,7 +12722,7 @@
       <c r="AH77" s="17"/>
       <c r="AI77" s="8"/>
     </row>
-    <row r="78" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="78" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A78" s="46">
         <v>2025</v>
       </c>
@@ -12788,7 +12822,7 @@
       <c r="AH78" s="12"/>
       <c r="AI78" s="8"/>
     </row>
-    <row r="79" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="79" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A79" s="46">
         <v>2025</v>
       </c>
@@ -12882,7 +12916,7 @@
       <c r="AH79" s="12"/>
       <c r="AI79" s="8"/>
     </row>
-    <row r="80" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="80" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A80" s="46">
         <v>2025</v>
       </c>
@@ -12974,7 +13008,7 @@
       <c r="AH80" s="17"/>
       <c r="AI80" s="8"/>
     </row>
-    <row r="81" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="81" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A81" s="46">
         <v>2025</v>
       </c>
@@ -13068,7 +13102,7 @@
       <c r="AH81" s="12"/>
       <c r="AI81" s="8"/>
     </row>
-    <row r="82" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="82" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A82" s="46">
         <v>2025</v>
       </c>
@@ -13156,7 +13190,7 @@
       <c r="AH82" s="17"/>
       <c r="AI82" s="8"/>
     </row>
-    <row r="83" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="83" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A83" s="46">
         <v>2025</v>
       </c>
@@ -13250,7 +13284,7 @@
       <c r="AH83" s="17"/>
       <c r="AI83" s="8"/>
     </row>
-    <row r="84" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="84" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A84" s="46">
         <v>2025</v>
       </c>
@@ -13344,7 +13378,7 @@
       <c r="AH84" s="17"/>
       <c r="AI84" s="8"/>
     </row>
-    <row r="85" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="85" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A85" s="46">
         <v>2025</v>
       </c>
@@ -13438,7 +13472,7 @@
       <c r="AH85" s="17"/>
       <c r="AI85" s="8"/>
     </row>
-    <row r="86" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="86" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A86" s="46">
         <v>2025</v>
       </c>
@@ -13536,7 +13570,7 @@
       <c r="AH86" s="17"/>
       <c r="AI86" s="8"/>
     </row>
-    <row r="87" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="87" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A87" s="46">
         <v>2025</v>
       </c>
@@ -13630,7 +13664,7 @@
       <c r="AH87" s="17"/>
       <c r="AI87" s="8"/>
     </row>
-    <row r="88" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="88" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A88" s="46">
         <v>2025</v>
       </c>
@@ -13724,7 +13758,7 @@
       <c r="AH88" s="17"/>
       <c r="AI88" s="8"/>
     </row>
-    <row r="89" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="89" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A89" s="46">
         <v>2025</v>
       </c>
@@ -13818,7 +13852,7 @@
       <c r="AH89" s="17"/>
       <c r="AI89" s="8"/>
     </row>
-    <row r="90" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="90" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A90" s="46">
         <v>2025</v>
       </c>
@@ -13914,7 +13948,7 @@
       <c r="AH90" s="17"/>
       <c r="AI90" s="8"/>
     </row>
-    <row r="91" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="91" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A91" s="46">
         <v>2025</v>
       </c>
@@ -14006,7 +14040,7 @@
       <c r="AH91" s="17"/>
       <c r="AI91" s="8"/>
     </row>
-    <row r="92" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="92" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A92" s="46">
         <v>2025</v>
       </c>
@@ -14067,7 +14101,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="Q92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14098,7 +14132,7 @@
       <c r="AH92" s="17"/>
       <c r="AI92" s="8"/>
     </row>
-    <row r="93" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="93" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A93" s="46">
         <v>2025</v>
       </c>
@@ -14186,7 +14220,7 @@
       <c r="AH93" s="17"/>
       <c r="AI93" s="8"/>
     </row>
-    <row r="94" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="94" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A94" s="46">
         <v>2025</v>
       </c>
@@ -14280,7 +14314,7 @@
       <c r="AH94" s="17"/>
       <c r="AI94" s="8"/>
     </row>
-    <row r="95" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="95" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A95" s="46">
         <v>2025</v>
       </c>
@@ -14374,7 +14408,7 @@
       <c r="AH95" s="17"/>
       <c r="AI95" s="8"/>
     </row>
-    <row r="96" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="96" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A96" s="46">
         <v>2025</v>
       </c>
@@ -14433,7 +14467,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="Q96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14464,7 +14498,7 @@
       <c r="AH96" s="17"/>
       <c r="AI96" s="8"/>
     </row>
-    <row r="97" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="97" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A97" s="46">
         <v>2025</v>
       </c>
@@ -14525,7 +14559,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="Q97" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14554,7 +14588,7 @@
       <c r="AH97" s="17"/>
       <c r="AI97" s="8"/>
     </row>
-    <row r="98" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="98" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A98" s="46">
         <v>2025</v>
       </c>
@@ -14656,7 +14690,7 @@
       <c r="AH98" s="17"/>
       <c r="AI98" s="8"/>
     </row>
-    <row r="99" spans="1:35" s="54" customFormat="1" ht="30" customHeight="1">
+    <row r="99" spans="1:35" s="54" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A99" s="53">
         <v>2026</v>
       </c>
@@ -14767,7 +14801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:35" s="60" customFormat="1" ht="30" customHeight="1">
+    <row r="100" spans="1:35" s="60" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A100" s="59">
         <v>2026</v>
       </c>
@@ -14876,7 +14910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
+    <row r="101" spans="1:35" s="65" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A101" s="60">
         <v>2026</v>
       </c>
@@ -14983,7 +15017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:35" s="60" customFormat="1" ht="30" customHeight="1">
+    <row r="102" spans="1:35" s="60" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A102" s="60">
         <v>2026</v>
       </c>
@@ -15013,7 +15047,7 @@
         <v>41</v>
       </c>
       <c r="J102" s="59" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="L102" s="59" t="s">
         <v>328</v>
@@ -15052,12 +15086,14 @@
       <c r="R102" s="59" t="s">
         <v>151</v>
       </c>
-      <c r="V102" s="110"/>
+      <c r="V102" s="110" t="s">
+        <v>329</v>
+      </c>
       <c r="W102" s="154" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="X102" s="60" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Y102" s="63"/>
       <c r="Z102" s="59"/>
@@ -15067,7 +15103,7 @@
       <c r="AF102" s="64"/>
       <c r="AG102" s="64"/>
     </row>
-    <row r="103" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
+    <row r="103" spans="1:35" s="65" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A103" s="60">
         <v>2026</v>
       </c>
@@ -15079,19 +15115,19 @@
         <v>35</v>
       </c>
       <c r="D103" s="60" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E103" s="60" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F103" s="60" t="s">
         <v>302</v>
       </c>
       <c r="G103" s="59" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H103" s="60" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I103" s="59" t="s">
         <v>51</v>
@@ -15100,7 +15136,7 @@
         <v>42</v>
       </c>
       <c r="K103" s="60" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L103" s="59" t="s">
         <v>43</v>
@@ -15143,14 +15179,14 @@
         <v>16552</v>
       </c>
       <c r="T103" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="U103" s="60"/>
       <c r="V103" s="110" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="W103" s="60" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="X103" s="60" t="s">
         <v>191</v>
@@ -15176,7 +15212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:35" s="60" customFormat="1" ht="30" customHeight="1">
+    <row r="104" spans="1:35" s="60" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A104" s="60">
         <v>2026</v>
       </c>
@@ -15200,7 +15236,7 @@
         <v>97</v>
       </c>
       <c r="H104" s="60" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I104" s="59" t="s">
         <v>41</v>
@@ -15247,10 +15283,10 @@
       </c>
       <c r="R104" s="59"/>
       <c r="V104" s="110" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="W104" s="60" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="X104" s="60" t="s">
         <v>314</v>
@@ -15274,7 +15310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
+    <row r="105" spans="1:35" s="65" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A105" s="60">
         <v>2026</v>
       </c>
@@ -15352,7 +15388,7 @@
       <c r="T105" s="60"/>
       <c r="U105" s="60"/>
       <c r="V105" s="110" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="W105" s="60" t="s">
         <v>323</v>
@@ -15373,7 +15409,7 @@
       <c r="AG105" s="64"/>
       <c r="AH105" s="60"/>
     </row>
-    <row r="106" spans="1:35" s="60" customFormat="1" ht="30" customHeight="1">
+    <row r="106" spans="1:35" s="60" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A106" s="60">
         <v>2026</v>
       </c>
@@ -15385,10 +15421,10 @@
         <v>35</v>
       </c>
       <c r="D106" s="60" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E106" s="60" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I106" s="59" t="s">
         <v>41</v>
@@ -15434,13 +15470,13 @@
         <v>OVER KPI</v>
       </c>
       <c r="R106" s="59" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="V106" s="110" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="W106" s="60" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="X106" s="60" t="s">
         <v>118</v>
@@ -15455,7 +15491,7 @@
       <c r="AF106" s="64"/>
       <c r="AG106" s="64"/>
     </row>
-    <row r="107" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
+    <row r="107" spans="1:35" s="65" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A107" s="60">
         <v>2026</v>
       </c>
@@ -15473,13 +15509,13 @@
         <v>253</v>
       </c>
       <c r="F107" s="60" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G107" s="60" t="s">
         <v>160</v>
       </c>
       <c r="H107" s="60" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I107" s="59" t="s">
         <v>41</v>
@@ -15531,16 +15567,16 @@
         <v>16733</v>
       </c>
       <c r="T107" s="60" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="U107" s="60">
         <v>16749</v>
       </c>
       <c r="V107" s="110" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="W107" s="60" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="X107" s="60" t="s">
         <v>118</v>
@@ -15558,7 +15594,7 @@
       <c r="AG107" s="64"/>
       <c r="AH107" s="60"/>
     </row>
-    <row r="108" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
+    <row r="108" spans="1:35" s="65" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A108" s="66">
         <v>2026</v>
       </c>
@@ -15570,19 +15606,19 @@
         <v>35</v>
       </c>
       <c r="D108" s="60" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E108" s="60" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F108" s="60" t="s">
         <v>302</v>
       </c>
       <c r="G108" s="60" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H108" s="60" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I108" s="59" t="s">
         <v>51</v>
@@ -15628,17 +15664,17 @@
         <v>ON KPI</v>
       </c>
       <c r="R108" s="59" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="S108" s="60">
         <v>16269</v>
       </c>
       <c r="T108" s="60" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="U108" s="60"/>
       <c r="V108" s="110" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="W108" s="60" t="s">
         <v>319</v>
@@ -15658,7 +15694,7 @@
       <c r="AF108" s="67"/>
       <c r="AG108" s="67"/>
     </row>
-    <row r="109" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
+    <row r="109" spans="1:35" s="65" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A109" s="66">
         <v>2026</v>
       </c>
@@ -15682,7 +15718,7 @@
         <v>104</v>
       </c>
       <c r="H109" s="60" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I109" s="59" t="s">
         <v>41</v>
@@ -15731,17 +15767,17 @@
         <v>151</v>
       </c>
       <c r="S109" s="60" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="T109" s="60" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="U109" s="60"/>
       <c r="V109" s="110" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="W109" s="60" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="X109" s="60" t="s">
         <v>314</v>
@@ -15758,7 +15794,7 @@
       <c r="AF109" s="68"/>
       <c r="AG109" s="68"/>
     </row>
-    <row r="110" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
+    <row r="110" spans="1:35" s="65" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A110" s="66">
         <v>2026</v>
       </c>
@@ -15770,10 +15806,10 @@
         <v>35</v>
       </c>
       <c r="D110" s="60" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E110" s="60" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F110" s="60" t="s">
         <v>87</v>
@@ -15782,7 +15818,7 @@
         <v>106</v>
       </c>
       <c r="H110" s="60" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I110" s="59" t="s">
         <v>41</v>
@@ -15828,20 +15864,20 @@
         <v>ON KPI</v>
       </c>
       <c r="R110" s="59" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="S110" s="60">
         <v>15917</v>
       </c>
       <c r="T110" s="60" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="U110" s="60"/>
       <c r="V110" s="110" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W110" s="60" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="X110" s="60" t="s">
         <v>314</v>
@@ -15858,10 +15894,10 @@
       <c r="AF110" s="68"/>
       <c r="AG110" s="68"/>
       <c r="AI110" s="69" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="111" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="111" spans="1:35" s="65" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A111" s="66">
         <v>2026</v>
       </c>
@@ -15873,10 +15909,10 @@
         <v>35</v>
       </c>
       <c r="D111" s="70" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E111" s="70" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F111" s="70" t="s">
         <v>87</v>
@@ -15897,7 +15933,7 @@
         <v>52</v>
       </c>
       <c r="L111" s="71" t="s">
-        <v>328</v>
+        <v>43</v>
       </c>
       <c r="M111" s="72">
         <v>46151</v>
@@ -15945,11 +15981,11 @@
         <v>15880</v>
       </c>
       <c r="V111" s="111" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="W111" s="70"/>
       <c r="X111" s="70" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Y111" s="74"/>
       <c r="Z111" s="71" t="s">
@@ -15964,7 +16000,7 @@
       <c r="AG111" s="67"/>
       <c r="AH111" s="76"/>
     </row>
-    <row r="112" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
+    <row r="112" spans="1:35" s="65" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A112" s="165">
         <v>2026</v>
       </c>
@@ -15976,10 +16012,10 @@
         <v>35</v>
       </c>
       <c r="D112" s="169" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E112" s="169" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F112" s="169" t="s">
         <v>90</v>
@@ -15988,7 +16024,7 @@
         <v>160</v>
       </c>
       <c r="H112" s="169" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I112" s="167" t="s">
         <v>41</v>
@@ -16000,7 +16036,7 @@
         <v>52</v>
       </c>
       <c r="L112" s="96" t="s">
-        <v>328</v>
+        <v>43</v>
       </c>
       <c r="M112" s="98">
         <v>46226</v>
@@ -16042,7 +16078,7 @@
         <v>ON KPI</v>
       </c>
       <c r="R112" s="167" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="S112" s="169">
         <v>15880</v>
@@ -16050,21 +16086,21 @@
       <c r="T112" s="169"/>
       <c r="U112" s="169"/>
       <c r="V112" s="174" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="W112" s="173">
         <v>46296</v>
       </c>
       <c r="X112" s="169" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Y112" s="175"/>
       <c r="Z112" s="167"/>
       <c r="AA112" s="167" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AB112" s="176" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AC112" s="177"/>
       <c r="AD112" s="177"/>
@@ -16073,10 +16109,10 @@
       <c r="AG112" s="103"/>
       <c r="AH112" s="178"/>
       <c r="AI112" s="179" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="113" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="113" spans="1:35" s="65" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A113" s="66">
         <v>2026</v>
       </c>
@@ -16160,10 +16196,10 @@
       <c r="T113" s="70"/>
       <c r="U113" s="70"/>
       <c r="V113" s="111" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="W113" s="154" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="X113" s="70" t="s">
         <v>314</v>
@@ -16174,7 +16210,7 @@
       </c>
       <c r="AA113" s="70"/>
       <c r="AB113" s="71" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AC113" s="75"/>
       <c r="AD113" s="75"/>
@@ -16183,10 +16219,10 @@
       <c r="AG113" s="67"/>
       <c r="AH113" s="76"/>
       <c r="AI113" s="69" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="114" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="114" spans="1:35" s="65" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A114" s="66">
         <v>2026</v>
       </c>
@@ -16198,10 +16234,10 @@
         <v>35</v>
       </c>
       <c r="D114" s="70" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E114" s="70" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F114" s="70" t="s">
         <v>178</v>
@@ -16210,7 +16246,7 @@
         <v>305</v>
       </c>
       <c r="H114" s="70" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I114" s="71" t="s">
         <v>41</v>
@@ -16270,9 +16306,11 @@
       <c r="T114" s="70"/>
       <c r="U114" s="70"/>
       <c r="V114" s="111" t="s">
-        <v>382</v>
-      </c>
-      <c r="W114" s="70"/>
+        <v>383</v>
+      </c>
+      <c r="W114" s="154" t="s">
+        <v>367</v>
+      </c>
       <c r="X114" s="70" t="s">
         <v>314</v>
       </c>
@@ -16282,7 +16320,7 @@
       </c>
       <c r="AA114" s="70"/>
       <c r="AB114" s="70" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AC114" s="75"/>
       <c r="AD114" s="75"/>
@@ -16291,10 +16329,10 @@
       <c r="AG114" s="67"/>
       <c r="AH114" s="76"/>
       <c r="AI114" s="45" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="115" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="115" spans="1:35" s="65" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A115" s="66">
         <v>2026</v>
       </c>
@@ -16306,10 +16344,10 @@
         <v>35</v>
       </c>
       <c r="D115" s="70" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E115" s="70" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F115" s="70" t="s">
         <v>302</v>
@@ -16376,7 +16414,7 @@
       <c r="T115" s="70"/>
       <c r="U115" s="76"/>
       <c r="V115" s="114" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="W115" s="116"/>
       <c r="X115" s="70" t="s">
@@ -16388,7 +16426,7 @@
       </c>
       <c r="AA115" s="70"/>
       <c r="AB115" s="60" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AC115" s="75"/>
       <c r="AD115" s="75"/>
@@ -16397,10 +16435,10 @@
       <c r="AG115" s="67"/>
       <c r="AH115" s="76"/>
       <c r="AI115" s="45" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="116" spans="1:35" s="76" customFormat="1" ht="30" customHeight="1">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="116" spans="1:35" s="76" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A116" s="66">
         <v>2026</v>
       </c>
@@ -16424,7 +16462,7 @@
         <v>269</v>
       </c>
       <c r="H116" s="70" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I116" s="71" t="s">
         <v>51</v>
@@ -16485,10 +16523,10 @@
       </c>
       <c r="T116" s="70"/>
       <c r="V116" s="115" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="W116" s="66" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="X116" s="70" t="s">
         <v>314</v>
@@ -16499,7 +16537,7 @@
       </c>
       <c r="AA116" s="70"/>
       <c r="AB116" s="60" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AC116" s="75"/>
       <c r="AD116" s="75"/>
@@ -16507,10 +16545,10 @@
       <c r="AF116" s="67"/>
       <c r="AG116" s="67"/>
       <c r="AI116" s="77" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="117" spans="1:35" s="105" customFormat="1" ht="30" customHeight="1">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="117" spans="1:35" s="105" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A117" s="95">
         <v>2026</v>
       </c>
@@ -16522,19 +16560,19 @@
         <v>35</v>
       </c>
       <c r="D117" s="97" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E117" s="97" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F117" s="97" t="s">
         <v>302</v>
       </c>
       <c r="G117" s="170" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H117" s="171" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I117" s="96" t="s">
         <v>51</v>
@@ -16594,11 +16632,11 @@
         <v>16748</v>
       </c>
       <c r="T117" s="97" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="U117" s="97"/>
       <c r="V117" s="112" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="W117" s="100">
         <v>46281</v>
@@ -16610,7 +16648,7 @@
       <c r="Z117" s="96"/>
       <c r="AA117" s="97"/>
       <c r="AB117" s="97" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AC117" s="102"/>
       <c r="AD117" s="102"/>
@@ -16619,10 +16657,10 @@
       <c r="AG117" s="103"/>
       <c r="AH117" s="104"/>
       <c r="AI117" s="106" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="118" spans="1:35" s="105" customFormat="1" ht="30" customHeight="1">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="118" spans="1:35" s="105" customFormat="1" ht="43.5" hidden="1" customHeight="1">
       <c r="A118" s="95">
         <v>2026</v>
       </c>
@@ -16637,7 +16675,7 @@
         <v>46</v>
       </c>
       <c r="E118" s="97" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F118" s="97" t="s">
         <v>61</v>
@@ -16646,7 +16684,7 @@
         <v>104</v>
       </c>
       <c r="H118" s="169" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I118" s="96" t="s">
         <v>41</v>
@@ -16698,17 +16736,17 @@
         <v>OVER KPI</v>
       </c>
       <c r="R118" s="96" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="S118" s="97">
         <v>15647</v>
       </c>
       <c r="T118" s="97" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="U118" s="97"/>
       <c r="V118" s="112" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="W118" s="100">
         <v>46281</v>
@@ -16720,7 +16758,7 @@
       <c r="Z118" s="96"/>
       <c r="AA118" s="97"/>
       <c r="AB118" s="96" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AC118" s="102"/>
       <c r="AD118" s="102"/>
@@ -16729,10 +16767,10 @@
       <c r="AG118" s="103"/>
       <c r="AH118" s="104"/>
       <c r="AI118" s="106" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="119" spans="1:35" s="105" customFormat="1" ht="30" customHeight="1">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="119" spans="1:35" s="105" customFormat="1" ht="43.5" customHeight="1">
       <c r="A119" s="116">
         <v>2026</v>
       </c>
@@ -16744,19 +16782,19 @@
         <v>35</v>
       </c>
       <c r="D119" s="168" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E119" s="70" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F119" s="70" t="s">
         <v>111</v>
       </c>
       <c r="G119" s="70" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H119" s="70" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I119" s="71" t="s">
         <v>51</v>
@@ -16768,7 +16806,7 @@
         <v>52</v>
       </c>
       <c r="L119" s="71" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M119" s="72">
         <v>46182</v>
@@ -16784,7 +16822,9 @@
 )</f>
         <v>46251</v>
       </c>
-      <c r="O119" s="74"/>
+      <c r="O119" s="74">
+        <v>46307</v>
+      </c>
       <c r="P119" s="71">
         <f ca="1">IF(M119="",                                                                                                                                                                                                   "",
    NETWORKDAYS(
@@ -16793,7 +16833,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="Q119" s="71" t="str">
         <f ca="1">IF(P119="",                                                                                                                                                                                                   "",
@@ -16814,21 +16854,21 @@
         <v>16124</v>
       </c>
       <c r="T119" s="70" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="U119" s="70"/>
       <c r="V119" s="111"/>
       <c r="W119" s="70"/>
       <c r="X119" s="70" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Y119" s="74"/>
       <c r="Z119" s="71"/>
       <c r="AA119" s="70" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AB119" s="70" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AC119" s="75"/>
       <c r="AD119" s="75"/>
@@ -16837,10 +16877,10 @@
       <c r="AG119" s="67"/>
       <c r="AH119" s="76"/>
       <c r="AI119" s="164" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="120" spans="1:35" ht="30" customHeight="1">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="120" spans="1:35" ht="43.5" customHeight="1">
       <c r="A120" s="95">
         <v>2026</v>
       </c>
@@ -16852,10 +16892,10 @@
         <v>45</v>
       </c>
       <c r="D120" s="181" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E120" s="97" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F120" s="97" t="s">
         <v>178</v>
@@ -16864,7 +16904,7 @@
         <v>179</v>
       </c>
       <c r="H120" s="97" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I120" s="96" t="s">
         <v>41</v>
@@ -16873,10 +16913,10 @@
         <v>42</v>
       </c>
       <c r="K120" s="97" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="L120" s="96" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="M120" s="162">
         <v>46260</v>
@@ -16901,7 +16941,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="Q120" s="96" t="str">
         <f ca="1">IF(P120="",                                                                                                                                                                                                   "",
@@ -16913,10 +16953,10 @@
       )
    )
 )</f>
-        <v>ON KPI</v>
+        <v>OVER KPI</v>
       </c>
       <c r="R120" s="96" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="S120" s="97">
         <v>16257</v>
@@ -16926,7 +16966,7 @@
       <c r="V120" s="97"/>
       <c r="W120" s="100"/>
       <c r="X120" s="97" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Y120" s="101"/>
       <c r="Z120" s="96"/>
@@ -16940,7 +16980,7 @@
       <c r="AH120" s="104"/>
       <c r="AI120" s="153"/>
     </row>
-    <row r="121" spans="1:35" ht="30" customHeight="1">
+    <row r="121" spans="1:35" ht="43.5" customHeight="1">
       <c r="A121" s="95">
         <v>2026</v>
       </c>
@@ -16952,10 +16992,10 @@
         <v>35</v>
       </c>
       <c r="D121" s="180" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E121" s="145" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F121" s="145" t="s">
         <v>302</v>
@@ -16974,7 +17014,7 @@
         <v>52</v>
       </c>
       <c r="L121" s="142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M121" s="152">
         <v>46280</v>
@@ -16999,7 +17039,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q121" s="142" t="str">
         <f ca="1">IF(P121="",                                                                                                                                                                                                   "",
@@ -17020,13 +17060,13 @@
         <v>16760</v>
       </c>
       <c r="T121" s="145" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U121" s="145"/>
       <c r="V121" s="145"/>
       <c r="W121" s="147"/>
       <c r="X121" s="145" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Y121" s="148"/>
       <c r="Z121" s="142"/>
@@ -17039,10 +17079,10 @@
       <c r="AG121" s="143"/>
       <c r="AH121" s="150"/>
       <c r="AI121" s="164" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="122" spans="1:35" ht="25.5" customHeight="1">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="122" spans="1:35" ht="43.5" hidden="1" customHeight="1">
       <c r="A122" s="95">
         <v>2026</v>
       </c>
@@ -17053,20 +17093,20 @@
       <c r="C122" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="D122" s="181" t="s">
-        <v>411</v>
+      <c r="D122" s="97" t="s">
+        <v>413</v>
       </c>
       <c r="E122" s="97" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F122" s="97" t="s">
         <v>87</v>
       </c>
       <c r="G122" s="97" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H122" s="97" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="I122" s="96" t="s">
         <v>41</v>
@@ -17078,7 +17118,7 @@
         <v>114</v>
       </c>
       <c r="L122" s="96" t="s">
-        <v>415</v>
+        <v>328</v>
       </c>
       <c r="M122" s="98">
         <v>46260</v>
@@ -17120,25 +17160,27 @@
         <v>ON KPI</v>
       </c>
       <c r="R122" s="96" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="S122" s="97">
         <v>16122</v>
       </c>
       <c r="T122" s="97" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="U122" s="97"/>
-      <c r="V122" s="97"/>
+      <c r="V122" s="97" t="s">
+        <v>419</v>
+      </c>
       <c r="W122" s="100"/>
       <c r="X122" s="97" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Y122" s="101"/>
       <c r="Z122" s="96"/>
       <c r="AA122" s="97"/>
       <c r="AB122" s="97" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AC122" s="102"/>
       <c r="AD122" s="102"/>
@@ -17147,10 +17189,10 @@
       <c r="AG122" s="103"/>
       <c r="AH122" s="104"/>
       <c r="AI122" s="106" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="123" spans="1:35" ht="20.25" customHeight="1">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="123" spans="1:35" ht="43.5" customHeight="1">
       <c r="A123" s="144">
         <v>2026</v>
       </c>
@@ -17162,10 +17204,10 @@
         <v>35</v>
       </c>
       <c r="D123" s="180" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E123" s="145" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F123" s="145" t="s">
         <v>178</v>
@@ -17174,7 +17216,7 @@
         <v>275</v>
       </c>
       <c r="H123" s="145" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I123" s="142" t="s">
         <v>41</v>
@@ -17182,9 +17224,11 @@
       <c r="J123" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="K123" s="145"/>
+      <c r="K123" s="145" t="s">
+        <v>52</v>
+      </c>
       <c r="L123" s="142" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="M123" s="152">
         <v>46279</v>
@@ -17200,7 +17244,9 @@
 )</f>
         <v>46323</v>
       </c>
-      <c r="O123" s="147"/>
+      <c r="O123" s="147">
+        <v>46311</v>
+      </c>
       <c r="P123" s="142">
         <f ca="1">IF(M123="",                                                                                                                                                                                                   "",
    NETWORKDAYS(
@@ -17209,7 +17255,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="Q123" s="142" t="str">
         <f ca="1">IF(P123="",                                                                                                                                                                                                   "",
@@ -17224,19 +17270,19 @@
         <v>ON KPI</v>
       </c>
       <c r="R123" s="142" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="S123" s="145">
         <v>15742</v>
       </c>
       <c r="T123" s="145" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="U123" s="145"/>
       <c r="V123" s="145"/>
       <c r="W123" s="147"/>
       <c r="X123" s="145" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Y123" s="148"/>
       <c r="Z123" s="142"/>
@@ -17249,10 +17295,10 @@
       <c r="AG123" s="143"/>
       <c r="AH123" s="150"/>
       <c r="AI123" s="164" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="124" spans="1:35" ht="20.25" customHeight="1">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="124" spans="1:35" ht="43.5" hidden="1" customHeight="1">
       <c r="A124" s="144">
         <v>2026</v>
       </c>
@@ -17264,10 +17310,10 @@
         <v>35</v>
       </c>
       <c r="D124" s="183" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E124" s="183" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F124" s="183"/>
       <c r="G124" s="183"/>
@@ -17278,7 +17324,9 @@
       <c r="J124" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="K124" s="183"/>
+      <c r="K124" s="183" t="s">
+        <v>72</v>
+      </c>
       <c r="L124" s="182" t="s">
         <v>328</v>
       </c>
@@ -17305,7 +17353,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Q124" s="182" t="str">
         <f ca="1">IF(P124="",                                                                                                                                                                                                   "",
@@ -17327,7 +17375,9 @@
       <c r="W124" s="186">
         <v>46388</v>
       </c>
-      <c r="X124" s="183"/>
+      <c r="X124" s="145" t="s">
+        <v>331</v>
+      </c>
       <c r="Y124" s="187"/>
       <c r="Z124" s="182"/>
       <c r="AA124" s="183"/>
@@ -17340,11 +17390,14 @@
       <c r="AH124" s="189"/>
       <c r="AI124" s="151"/>
     </row>
-    <row r="125" spans="1:35" ht="20.25" customHeight="1">
+    <row r="125" spans="1:35" ht="43.5" hidden="1" customHeight="1">
       <c r="A125" s="144">
         <v>2026</v>
       </c>
-      <c r="B125" s="142"/>
+      <c r="B125" s="182" t="str">
+        <f>IF(M125="", "", TEXT(M125, "[$-en-US]mmm"))</f>
+        <v>Sep</v>
+      </c>
       <c r="C125" s="142" t="s">
         <v>35</v>
       </c>
@@ -17352,7 +17405,7 @@
         <v>77</v>
       </c>
       <c r="E125" s="145" t="s">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="F125" s="145"/>
       <c r="G125" s="145"/>
@@ -17363,7 +17416,9 @@
       <c r="J125" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="K125" s="145"/>
+      <c r="K125" s="145" t="s">
+        <v>72</v>
+      </c>
       <c r="L125" s="142" t="s">
         <v>328</v>
       </c>
@@ -17381,7 +17436,9 @@
 )</f>
         <v>46323</v>
       </c>
-      <c r="O125" s="147"/>
+      <c r="O125" s="147">
+        <v>46324</v>
+      </c>
       <c r="P125" s="142">
         <f ca="1">IF(M125="",                                                                                                                                                                                                   "",
    NETWORKDAYS(
@@ -17390,7 +17447,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="Q125" s="142" t="str">
         <f ca="1">IF(P125="",                                                                                                                                                                                                   "",
@@ -17402,15 +17459,21 @@
       )
    )
 )</f>
-        <v>ON KPI</v>
-      </c>
-      <c r="R125" s="142"/>
+        <v>OVER KPI</v>
+      </c>
+      <c r="R125" s="142" t="s">
+        <v>345</v>
+      </c>
       <c r="S125" s="145"/>
       <c r="T125" s="145"/>
       <c r="U125" s="145"/>
       <c r="V125" s="145"/>
-      <c r="W125" s="147"/>
-      <c r="X125" s="145"/>
+      <c r="W125" s="147">
+        <v>46388</v>
+      </c>
+      <c r="X125" s="145" t="s">
+        <v>331</v>
+      </c>
       <c r="Y125" s="148"/>
       <c r="Z125" s="142"/>
       <c r="AA125" s="145"/>
@@ -17707,7 +17770,7 @@
         <v>314</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="84.6" thickBot="1">
@@ -17718,7 +17781,7 @@
         <v>82</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
@@ -17748,7 +17811,7 @@
         <v>191</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="105.6" thickBot="1">
@@ -17782,7 +17845,7 @@
         <v>46032</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>446</v>
@@ -17797,7 +17860,7 @@
         <v>448</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>449</v>
@@ -17826,7 +17889,7 @@
         <v>72</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42.6" thickBot="1">
@@ -18101,7 +18164,7 @@
         <v>46116</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>480</v>
@@ -18732,7 +18795,7 @@
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>293</v>
@@ -18759,7 +18822,7 @@
         <v>539</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="63.6" thickBot="1">
@@ -18840,7 +18903,7 @@
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>68</v>
@@ -18924,7 +18987,7 @@
       </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>98</v>
@@ -18972,7 +19035,7 @@
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>113</v>
@@ -19008,7 +19071,7 @@
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>69</v>
@@ -19178,7 +19241,7 @@
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
       <c r="L117" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="118" spans="1:12" ht="63.6" thickBot="1">
@@ -19402,7 +19465,7 @@
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
       <c r="L149" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="150" spans="10:12" ht="63.6" thickBot="1">
@@ -19416,14 +19479,14 @@
       <c r="J151" s="2"/>
       <c r="K151" s="2"/>
       <c r="L151" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="152" spans="10:12" ht="42.6" thickBot="1">
       <c r="J152" s="2"/>
       <c r="K152" s="2"/>
       <c r="L152" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="153" spans="10:12" ht="42.6" thickBot="1">
@@ -19465,56 +19528,56 @@
       <c r="J158" s="2"/>
       <c r="K158" s="2"/>
       <c r="L158" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="159" spans="10:12" ht="63.6" thickBot="1">
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
       <c r="L159" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="160" spans="10:12" ht="42">
       <c r="J160" s="2"/>
       <c r="K160" s="2"/>
       <c r="L160" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="161" spans="10:12" ht="42">
       <c r="J161" s="2"/>
       <c r="K161" s="2"/>
       <c r="L161" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="162" spans="10:12" ht="42">
       <c r="J162" s="2"/>
       <c r="K162" s="2"/>
       <c r="L162" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="163" spans="10:12" ht="63">
       <c r="J163" s="2"/>
       <c r="K163" s="2"/>
       <c r="L163" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="164" spans="10:12" ht="82.5">
       <c r="J164" s="2"/>
       <c r="K164" s="2"/>
       <c r="L164" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" spans="10:12" ht="82.5">
       <c r="J165" s="2"/>
       <c r="K165" s="2"/>
       <c r="L165" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="166" spans="10:12" ht="62.25">
@@ -19528,7 +19591,7 @@
       <c r="J167" s="2"/>
       <c r="K167" s="2"/>
       <c r="L167" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" spans="10:12" ht="21.6" thickBot="1">
@@ -24350,7 +24413,7 @@
       <c r="I14" s="122"/>
       <c r="J14" s="122"/>
       <c r="K14" s="122" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L14" s="122">
         <v>7</v>
@@ -24416,7 +24479,7 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" s="199" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B16" s="126" t="s">
         <v>589</v>
@@ -25233,7 +25296,7 @@
         <v>442</v>
       </c>
       <c r="D37" s="134" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E37" s="135" t="s">
         <v>619</v>
